--- a/data/trans_orig/P57B1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57B1_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido deprimido en 2023</t>
+          <t>Población según se ha sentido deprimido en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1032</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1327</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>848</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9957</t>
+          <t>10628</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16176</t>
+          <t>15812</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39190</t>
+          <t>40840</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67835</t>
+          <t>69068</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43040</t>
+          <t>43842</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68388</t>
+          <t>69400</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>90039</t>
+          <t>88646</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>130042</t>
+          <t>127535</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>238616</t>
+          <t>237885</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>268762</t>
+          <t>268283</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>214650</t>
+          <t>215961</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>240796</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>462420</t>
+          <t>462753</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>502495</t>
+          <t>503722</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,8%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18307</t>
+          <t>18141</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10581</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27068</t>
+          <t>27409</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16737</t>
+          <t>17098</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12519</t>
+          <t>12079</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>25362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18770</t>
+          <t>18667</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37086</t>
+          <t>36352</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>111357</t>
+          <t>109750</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>164425</t>
+          <t>162679</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138890</t>
+          <t>138879</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>174936</t>
+          <t>175566</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>258321</t>
+          <t>260651</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>321697</t>
+          <t>322309</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>331537</t>
+          <t>336308</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>386652</t>
+          <t>389809</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>310971</t>
+          <t>312890</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349393</t>
+          <t>350969</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>661235</t>
+          <t>662802</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>726921</t>
+          <t>726554</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,63%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>10822</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7357</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17401</t>
+          <t>17403</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11961</t>
+          <t>12464</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25140</t>
+          <t>24585</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>9386</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22910</t>
+          <t>23499</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20456</t>
+          <t>20211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36252</t>
+          <t>35440</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>33031</t>
+          <t>32586</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>53858</t>
+          <t>53614</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35216</t>
+          <t>35697</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58639</t>
+          <t>59088</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72684</t>
+          <t>73124</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99803</t>
+          <t>101641</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114263</t>
+          <t>112519</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>149845</t>
+          <t>148206</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>231912</t>
+          <t>232539</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>259387</t>
+          <t>259929</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>206830</t>
+          <t>207525</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>237151</t>
+          <t>237803</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>452141</t>
+          <t>450092</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>491180</t>
+          <t>491096</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2253</t>
+          <t>2213</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13616</t>
+          <t>13548</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24419</t>
+          <t>24982</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10638</t>
+          <t>10371</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31414</t>
+          <t>30209</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16737</t>
+          <t>15770</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>15962</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38756</t>
+          <t>38172</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22586</t>
+          <t>24295</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45793</t>
+          <t>47091</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>50438</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>82861</t>
+          <t>84206</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52924</t>
+          <t>52995</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>109623</t>
+          <t>108239</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>109037</t>
+          <t>110437</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>177187</t>
+          <t>177003</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>212226</t>
+          <t>209249</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>246836</t>
+          <t>245360</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>315454</t>
+          <t>314543</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>394180</t>
+          <t>394880</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>544036</t>
+          <t>544965</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>634856</t>
+          <t>630162</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>80,72%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2553</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>10662</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>16790</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13792</t>
+          <t>12965</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15020</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12971</t>
+          <t>13461</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24567</t>
+          <t>25184</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>75305</t>
+          <t>74927</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>98890</t>
+          <t>97317</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>102510</t>
+          <t>101680</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>122344</t>
+          <t>122777</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>183168</t>
+          <t>182529</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>213580</t>
+          <t>213740</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,28%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>67504</t>
+          <t>68160</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>90113</t>
+          <t>89987</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>68549</t>
+          <t>70050</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>89995</t>
+          <t>90876</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>143652</t>
+          <t>142957</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>174070</t>
+          <t>174992</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,26%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15319</t>
+          <t>15198</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11841</t>
+          <t>11739</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>10784</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>23148</t>
+          <t>22920</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10627</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23103</t>
+          <t>24488</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>16624</t>
+          <t>16669</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>29256</t>
+          <t>29120</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>30679</t>
+          <t>30742</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>48934</t>
+          <t>49019</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>34969</t>
+          <t>35340</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>56577</t>
+          <t>55796</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>41041</t>
+          <t>41944</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>59913</t>
+          <t>60611</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>82586</t>
+          <t>82210</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>110586</t>
+          <t>111653</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>185753</t>
+          <t>185129</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>210209</t>
+          <t>210217</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>165447</t>
+          <t>164169</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>187989</t>
+          <t>186306</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>356705</t>
+          <t>357222</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>391521</t>
+          <t>390946</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,34%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>20513</t>
+          <t>20327</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7297</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26033</t>
+          <t>25692</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>17567</t>
+          <t>16492</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>41327</t>
+          <t>40495</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>23972</t>
+          <t>23997</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>49289</t>
+          <t>49166</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>21346</t>
+          <t>23242</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>70828</t>
+          <t>70830</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>48035</t>
+          <t>48377</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>105076</t>
+          <t>105884</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>130434</t>
+          <t>131053</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>181727</t>
+          <t>179251</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>300297</t>
+          <t>301467</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>638712</t>
+          <t>640947</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>441246</t>
+          <t>441541</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>902613</t>
+          <t>960118</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>65,25%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>395761</t>
+          <t>395865</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>449459</t>
+          <t>449628</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>172854</t>
+          <t>169629</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>460196</t>
+          <t>460124</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>496586</t>
+          <t>446062</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>902023</t>
+          <t>901078</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,23%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>33131</t>
+          <t>34133</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>29553</t>
+          <t>29315</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>48635</t>
+          <t>48306</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>36602</t>
+          <t>37135</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>75245</t>
+          <t>76498</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>35190</t>
+          <t>39868</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>121466</t>
+          <t>121826</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>104779</t>
+          <t>103828</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>138036</t>
+          <t>136516</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>130376</t>
+          <t>125298</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>249242</t>
+          <t>249595</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>160697</t>
+          <t>162015</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>499322</t>
+          <t>496020</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>375639</t>
+          <t>376717</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>421298</t>
+          <t>422843</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>472819</t>
+          <t>464212</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>899103</t>
+          <t>901493</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,75%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>286684</t>
+          <t>286743</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>723378</t>
+          <t>718493</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>143820</t>
+          <t>141761</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>183967</t>
+          <t>181760</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>437802</t>
+          <t>436079</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1004293</t>
+          <t>1020032</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>61,95%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>52067</t>
+          <t>53927</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>88433</t>
+          <t>89409</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>78644</t>
+          <t>79609</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>116219</t>
+          <t>118046</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>141203</t>
+          <t>140650</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>195298</t>
+          <t>190786</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>141458</t>
+          <t>137460</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>206825</t>
+          <t>206484</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>226465</t>
+          <t>232016</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>311066</t>
+          <t>312613</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>400313</t>
+          <t>392413</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>505811</t>
+          <t>504889</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>743946</t>
+          <t>729565</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1034568</t>
+          <t>1037985</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1223061</t>
+          <t>1217813</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1793914</t>
+          <t>1736718</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2086998</t>
+          <t>2085068</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2860748</t>
+          <t>2779459</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>39,13%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2152979</t>
+          <t>2148417</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2523504</t>
+          <t>2526586</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1559751</t>
+          <t>1606274</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2039803</t>
+          <t>2042571</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>3780572</t>
+          <t>3819303</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4441594</t>
+          <t>4456540</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57B1_2023-Provincia-trans_orig.xlsx
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>793</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>9221</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15812</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53121</t>
+          <t>54490</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40840</t>
+          <t>41635</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69068</t>
+          <t>68997</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>53929</t>
+          <t>57621</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43842</t>
+          <t>47651</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>69400</t>
+          <t>71032</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>107051</t>
+          <t>112112</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>88646</t>
+          <t>94823</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>127535</t>
+          <t>128180</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>254787</t>
+          <t>261258</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>237885</t>
+          <t>246700</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>268283</t>
+          <t>273677</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>230019</t>
+          <t>252330</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>215961</t>
+          <t>239243</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>241494</t>
+          <t>262919</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>484805</t>
+          <t>513589</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>462753</t>
+          <t>496426</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>503722</t>
+          <t>531074</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,65%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>18355</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7523</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>13859</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>16723</t>
+          <t>17061</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10451</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27409</t>
+          <t>26077</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -1407,27 +1407,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17098</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1442,22 +1442,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18013</t>
+          <t>19147</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12079</t>
+          <t>12854</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25362</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>26549</t>
+          <t>28058</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18667</t>
+          <t>19738</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36352</t>
+          <t>39466</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>135156</t>
+          <t>136001</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>109750</t>
+          <t>113163</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>162679</t>
+          <t>165629</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>155716</t>
+          <t>166223</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138879</t>
+          <t>147031</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>175566</t>
+          <t>185894</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,22 +1590,22 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>290872</t>
+          <t>302224</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>260651</t>
+          <t>271781</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>322309</t>
+          <t>333751</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>363293</t>
+          <t>374086</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>336308</t>
+          <t>345963</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>389809</t>
+          <t>396473</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>331304</t>
+          <t>350965</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>312890</t>
+          <t>331283</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>350969</t>
+          <t>370690</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>694597</t>
+          <t>725052</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>662802</t>
+          <t>693953</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>726554</t>
+          <t>756894</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,58%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>516184</t>
+          <t>528402</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>516184</t>
+          <t>528402</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>516184</t>
+          <t>528402</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>512557</t>
+          <t>543992</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>512557</t>
+          <t>543992</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>512557</t>
+          <t>543992</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1028741</t>
+          <t>1072395</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1028741</t>
+          <t>1072395</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1028741</t>
+          <t>1072395</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,102 +1863,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>12693</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>7954</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>19203</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>5,41%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>18481</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>12389</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>25181</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>1,85%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>11811</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>7507</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>17403</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>17625</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>12464</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>24585</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15131</t>
+          <t>14928</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9386</t>
+          <t>9601</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23499</t>
+          <t>23428</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27306</t>
+          <t>29370</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20211</t>
+          <t>22007</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35440</t>
+          <t>37597</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>42436</t>
+          <t>44298</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>32586</t>
+          <t>35271</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>53614</t>
+          <t>55714</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>45400</t>
+          <t>48188</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35697</t>
+          <t>36959</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59088</t>
+          <t>61071</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>85400</t>
+          <t>86894</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73124</t>
+          <t>72252</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101641</t>
+          <t>100511</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>130800</t>
+          <t>135081</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>112519</t>
+          <t>117712</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>148206</t>
+          <t>154493</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>247685</t>
+          <t>245177</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>232539</t>
+          <t>230769</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>259929</t>
+          <t>258215</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>223273</t>
+          <t>226047</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>207525</t>
+          <t>210283</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>237803</t>
+          <t>242229</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>470958</t>
+          <t>471224</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>450092</t>
+          <t>447743</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>491096</t>
+          <t>490212</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>73,27%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>314029</t>
+          <t>314080</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>314029</t>
+          <t>314080</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>314029</t>
+          <t>314080</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>347790</t>
+          <t>355004</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>347790</t>
+          <t>355004</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>347790</t>
+          <t>355004</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>661819</t>
+          <t>669084</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>661819</t>
+          <t>669084</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>661819</t>
+          <t>669084</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12310</t>
+          <t>14030</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>8122</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24982</t>
+          <t>26718</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>18267</t>
+          <t>20584</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10371</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30209</t>
+          <t>35677</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15770</t>
+          <t>16607</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>26160</t>
+          <t>27680</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15962</t>
+          <t>20546</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38172</t>
+          <t>37464</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>34079</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24295</t>
+          <t>26864</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>47091</t>
+          <t>47257</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>65079</t>
+          <t>72310</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50438</t>
+          <t>55438</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>84206</t>
+          <t>93530</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>83518</t>
+          <t>96416</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52995</t>
+          <t>81888</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>108239</t>
+          <t>112749</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>148597</t>
+          <t>168726</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>110437</t>
+          <t>147885</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>177003</t>
+          <t>195372</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>229838</t>
+          <t>282092</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>209249</t>
+          <t>260890</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>245360</t>
+          <t>300727</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>349929</t>
+          <t>279806</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>314543</t>
+          <t>262907</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>394880</t>
+          <t>297239</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>579766</t>
+          <t>561898</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>544965</t>
+          <t>533345</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>630162</t>
+          <t>588212</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>308792</t>
+          <t>369089</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>308792</t>
+          <t>369089</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>308792</t>
+          <t>369089</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>471917</t>
+          <t>417932</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>471917</t>
+          <t>417932</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>471917</t>
+          <t>417932</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>780709</t>
+          <t>787021</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>780709</t>
+          <t>787021</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>780709</t>
+          <t>787021</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>12867</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>10730</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16790</t>
+          <t>18727</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>7956</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12965</t>
+          <t>15237</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>10535</t>
+          <t>11384</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7832</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>15996</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>18491</t>
+          <t>19986</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13461</t>
+          <t>14593</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25184</t>
+          <t>26890</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>86251</t>
+          <t>101031</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>74927</t>
+          <t>88514</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>97317</t>
+          <t>113492</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>112505</t>
+          <t>121588</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>101680</t>
+          <t>110426</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>122777</t>
+          <t>131338</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>198755</t>
+          <t>222619</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>182529</t>
+          <t>205326</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>213740</t>
+          <t>238018</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,08%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>79139</t>
+          <t>89439</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>68160</t>
+          <t>77062</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>89987</t>
+          <t>101738</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>79550</t>
+          <t>87864</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>70050</t>
+          <t>78037</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>90876</t>
+          <t>98742</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>158690</t>
+          <t>177303</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>142957</t>
+          <t>161054</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>174992</t>
+          <t>195098</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>207924</t>
+          <t>226435</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>207924</t>
+          <t>226435</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>207924</t>
+          <t>226435</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>386666</t>
+          <t>432100</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>386666</t>
+          <t>432100</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>386666</t>
+          <t>432100</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>8948</t>
+          <t>8717</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15198</t>
+          <t>14700</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11739</t>
+          <t>11868</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>16380</t>
+          <t>16309</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10784</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22920</t>
+          <t>23059</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>16363</t>
+          <t>17457</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11337</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24488</t>
+          <t>25356</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>22561</t>
+          <t>23762</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>16669</t>
+          <t>18140</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>29120</t>
+          <t>31514</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>41219</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>30742</t>
+          <t>33410</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>49019</t>
+          <t>51611</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>44795</t>
+          <t>46951</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>35340</t>
+          <t>37214</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>55796</t>
+          <t>57774</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>50721</t>
+          <t>53199</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>41944</t>
+          <t>44370</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>60611</t>
+          <t>63468</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>95516</t>
+          <t>100150</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>82210</t>
+          <t>86274</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>111653</t>
+          <t>115924</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>198763</t>
+          <t>196829</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>185129</t>
+          <t>184055</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>210217</t>
+          <t>209300</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>176341</t>
+          <t>179197</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>164169</t>
+          <t>167393</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>186306</t>
+          <t>190194</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>375103</t>
+          <t>376026</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>357222</t>
+          <t>359022</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>390946</t>
+          <t>393060</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>73,65%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>268869</t>
+          <t>269954</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>268869</t>
+          <t>269954</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>268869</t>
+          <t>269954</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>525924</t>
+          <t>533704</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>525924</t>
+          <t>533704</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>525924</t>
+          <t>533704</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>12407</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>20327</t>
+          <t>21869</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>16559</t>
+          <t>20978</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>14053</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25692</t>
+          <t>30046</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>28369</t>
+          <t>33385</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>16492</t>
+          <t>23423</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>40495</t>
+          <t>45337</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>34003</t>
+          <t>43379</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>23997</t>
+          <t>30413</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>49166</t>
+          <t>60077</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>48413</t>
+          <t>54427</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>23242</t>
+          <t>41574</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>70830</t>
+          <t>68258</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>82416</t>
+          <t>97806</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>48377</t>
+          <t>77864</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>105884</t>
+          <t>118216</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>155299</t>
+          <t>180861</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>131053</t>
+          <t>155255</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>179251</t>
+          <t>207234</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>440186</t>
+          <t>276124</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>301467</t>
+          <t>249731</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>640947</t>
+          <t>299970</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>595485</t>
+          <t>456985</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>441541</t>
+          <t>421195</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>960118</t>
+          <t>493951</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>423168</t>
+          <t>483039</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>395865</t>
+          <t>456544</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>449628</t>
+          <t>513885</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>342090</t>
+          <t>418426</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>169629</t>
+          <t>395257</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>460124</t>
+          <t>446564</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>765258</t>
+          <t>901464</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>446062</t>
+          <t>860150</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>901078</t>
+          <t>941957</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>63,23%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>847249</t>
+          <t>769954</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>847249</t>
+          <t>769954</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>847249</t>
+          <t>769954</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1471528</t>
+          <t>1489641</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1471528</t>
+          <t>1489641</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1471528</t>
+          <t>1489641</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>21663</t>
+          <t>27242</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>18771</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>34133</t>
+          <t>37968</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>37638</t>
+          <t>45063</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>29315</t>
+          <t>34328</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>48306</t>
+          <t>56653</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>59301</t>
+          <t>72305</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>37135</t>
+          <t>59632</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>76498</t>
+          <t>87836</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>83897</t>
+          <t>94740</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>39868</t>
+          <t>78737</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>121826</t>
+          <t>116427</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>120052</t>
+          <t>139569</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>103828</t>
+          <t>122623</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>136516</t>
+          <t>160784</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>234308</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>125298</t>
+          <t>211519</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>249595</t>
+          <t>261116</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>358001</t>
+          <t>417509</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>162015</t>
+          <t>387088</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>496020</t>
+          <t>449968</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>397611</t>
+          <t>455075</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>376717</t>
+          <t>427977</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>422843</t>
+          <t>481295</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>755612</t>
+          <t>872584</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>464212</t>
+          <t>835979</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>901493</t>
+          <t>916554</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>56,25%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>465160</t>
+          <t>258582</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>286743</t>
+          <t>226843</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>718493</t>
+          <t>289170</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>162430</t>
+          <t>191624</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>141761</t>
+          <t>168864</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>181760</t>
+          <t>216249</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>627590</t>
+          <t>450206</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>436079</t>
+          <t>413513</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1020032</t>
+          <t>488814</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>30,0%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>68786</t>
+          <t>76707</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>53927</t>
+          <t>60583</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>89409</t>
+          <t>96189</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>98610</t>
+          <t>113610</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>79609</t>
+          <t>97648</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>118046</t>
+          <t>134337</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>167395</t>
+          <t>190317</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>140650</t>
+          <t>166970</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>190786</t>
+          <t>216207</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>177339</t>
+          <t>199246</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>137460</t>
+          <t>175465</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>206484</t>
+          <t>227486</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>278726</t>
+          <t>311448</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>232016</t>
+          <t>283509</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>312613</t>
+          <t>341646</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>456065</t>
+          <t>510694</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>392413</t>
+          <t>474432</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>504889</t>
+          <t>553907</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>943101</t>
+          <t>1057340</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>729565</t>
+          <t>1000549</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1037985</t>
+          <t>1119213</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1379587</t>
+          <t>1313142</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1217813</t>
+          <t>1266341</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1736718</t>
+          <t>1371876</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,17 +5573,17 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>2322688</t>
+          <t>2370482</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2085068</t>
+          <t>2291310</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2779459</t>
+          <t>2453396</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>33,85%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2261832</t>
+          <t>2190502</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2148417</t>
+          <t>2126657</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2526586</t>
+          <t>2252364</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>1894936</t>
+          <t>1986260</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1606274</t>
+          <t>1933503</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2042571</t>
+          <t>2038487</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>4156768</t>
+          <t>4176762</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>3819303</t>
+          <t>4089823</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4456540</t>
+          <t>4256625</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>58,73%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3451058</t>
+          <t>3523794</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3451058</t>
+          <t>3523794</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3451058</t>
+          <t>3523794</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3651858</t>
+          <t>3724460</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3651858</t>
+          <t>3724460</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3651858</t>
+          <t>3724460</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7102916</t>
+          <t>7248254</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7102916</t>
+          <t>7248254</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7102916</t>
+          <t>7248254</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
